--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_78_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_78_R8.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5149</v>
+        <v>8.0517</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5722</v>
+        <v>6.0754</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9428</v>
+        <v>1.9764</v>
       </c>
       <c r="G2" t="n">
         <v>4.0162</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0864</v>
+        <v>-0.5496</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8883</v>
+        <v>-0.3851</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1981</v>
+        <v>-0.1645</v>
       </c>
       <c r="V2" t="n">
         <v>2.0336</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0204</v>
+        <v>5.1361</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3565</v>
+        <v>2.5058</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6639</v>
+        <v>2.6303</v>
       </c>
       <c r="G3" t="n">
         <v>1.8964</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9643</v>
+        <v>1.08</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5034</v>
+        <v>0.6528</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4608</v>
+        <v>0.4272</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2789</v>
+        <v>4.5216</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8328</v>
+        <v>0.9075</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4461</v>
+        <v>3.6141</v>
       </c>
       <c r="G4" t="n">
         <v>4.5048</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1357</v>
+        <v>0.107</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1142</v>
+        <v>0.1889</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.25</v>
+        <v>-0.0819</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7446</v>
+        <v>2.2534</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2788</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0234</v>
+        <v>3.0906</v>
       </c>
       <c r="G5" t="n">
         <v>1.2537</v>
@@ -844,13 +844,13 @@
         <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>0.434</v>
+        <v>-0.0571</v>
       </c>
       <c r="T5" t="n">
-        <v>0.767</v>
+        <v>0.2087</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.333</v>
+        <v>-0.2658</v>
       </c>
       <c r="V5" t="n">
         <v>2.6805</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2852</v>
+        <v>1.7473</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3406</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6257</v>
+        <v>1.6593</v>
       </c>
       <c r="G6" t="n">
         <v>3.3691</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5478</v>
+        <v>-0.0857</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8215</v>
+        <v>-0.393</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2737</v>
+        <v>0.3073</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6826</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0.6573</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0253</v>
+        <v>0.1598</v>
       </c>
       <c r="G7" t="n">
         <v>0.8996</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.217</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0677</v>
+        <v>0.0668</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6856</v>
+        <v>-1.2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1586</v>
+        <v>-0.1206</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8442</v>
+        <v>-1.0794</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9381</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6805</v>
+        <v>0.1661</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1889</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4916</v>
+        <v>0.2563</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3558</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9283</v>
+        <v>-1.6693</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5909</v>
+        <v>0.2486</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3373</v>
+        <v>-1.9178</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0625</v>
+        <v>-1.0172</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8618</v>
+        <v>0.2977</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.9243</v>
+        <v>-1.3149</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6049</v>
+        <v>0.3193</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1078</v>
+        <v>0.3193</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7127</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4576</v>
+        <v>-1.3365</v>
       </c>
       <c r="N10" t="n">
-        <v>0.754</v>
+        <v>-0.0216</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.2116</v>
+        <v>-1.3149</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7062</v>
+        <v>0.116</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2819</v>
+        <v>0.1612</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4244</v>
+        <v>-0.0452</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2836</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0471</v>
+        <v>-2.3687</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.062</v>
+        <v>-2.0313</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9851</v>
+        <v>-0.3373</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0172</v>
+        <v>-2.0625</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2977</v>
+        <v>0.8618</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3149</v>
+        <v>-2.9243</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3193</v>
+        <v>-0.6049</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3193</v>
+        <v>0.1078</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.7127</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3365</v>
+        <v>-1.4576</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0216</v>
+        <v>0.754</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3149</v>
+        <v>-2.2116</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2618</v>
+        <v>1.2658</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1494</v>
+        <v>0.8415</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1125</v>
+        <v>0.4244</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5361</v>
+        <v>0.2836</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1686</v>
+        <v>-2.8841</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8437</v>
+        <v>-0.4584</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3249</v>
+        <v>-2.4257</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4723</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9282</v>
+        <v>-0.6438</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.507</v>
+        <v>-0.1217</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4213</v>
+        <v>-0.5221</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3708</v>
+        <v>-2.9587</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.2048</v>
+        <v>-2.6583</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.166</v>
+        <v>-0.3004</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0176</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3532</v>
+        <v>0.0589</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3576</v>
+        <v>0.1889</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0044</v>
+        <v>-0.13</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1582</v>
+        <v>11.2783</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2566</v>
+        <v>4.376799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>6.901699999999998</v>
+        <v>6.901899999999999</v>
       </c>
       <c r="G14" t="n">
         <v>8.264099999999999</v>
@@ -1534,10 +1534,10 @@
         <v>1.7122</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.6776</v>
+        <v>-7.677599999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2367</v>
@@ -1546,13 +1546,13 @@
         <v>16.2369</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2549</v>
+        <v>1.375</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.01779999999999998</v>
+        <v>1.1025</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2723</v>
+        <v>0.2725</v>
       </c>
       <c r="V14" t="n">
         <v>1.639299999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.6021</v>
+        <v>6.5291</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6721</v>
+        <v>6.3746</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1545</v>
       </c>
       <c r="G15" t="n">
         <v>3.6388</v>
@@ -1624,13 +1624,13 @@
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8732</v>
+        <v>0.8002</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8758</v>
+        <v>0.5783</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0026</v>
+        <v>0.2219</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9887</v>
+        <v>0.7192</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7255</v>
+        <v>1.4896</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7368</v>
+        <v>-0.7704</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4302</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0092</v>
+        <v>-0.2603</v>
       </c>
       <c r="T16" t="n">
-        <v>0.311</v>
+        <v>0.0751</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3018</v>
+        <v>-0.3354</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6778999999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2044</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3137</v>
+        <v>-0.363</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5181</v>
+        <v>0.2693</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.849</v>
+        <v>-1.8101</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5162</v>
+        <v>-2.5594</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3652</v>
+        <v>0.7493</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2486</v>
+        <v>0.8246</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.4566</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7863</v>
+        <v>1.2811</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6004</v>
+        <v>-2.6347</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0216</v>
+        <v>-2.1028</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5788</v>
+        <v>-0.5319</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>3.0154</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3224</v>
+        <v>-0.5001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5623</v>
+        <v>-0.3888</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2399</v>
+        <v>-0.1114</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>2.6805</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2078</v>
+        <v>-0.1177</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5493</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3415</v>
+        <v>0.4315</v>
       </c>
       <c r="G18" t="n">
         <v>0.3009</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0448</v>
+        <v>0.0452</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2161</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1713</v>
+        <v>0.2614</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6657</v>
+        <v>-0.6762</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5425</v>
+        <v>-0.1581</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1232</v>
+        <v>-0.5181</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8101</v>
+        <v>-0.849</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5594</v>
+        <v>0.5162</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7493</v>
+        <v>-1.3652</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8246</v>
+        <v>-0.2486</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4566</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2811</v>
+        <v>-0.7863</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6347</v>
+        <v>-0.6004</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.1028</v>
+        <v>-0.0216</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5319</v>
+        <v>-0.5788</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0154</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0722</v>
+        <v>-0.1494</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5683</v>
+        <v>0.0905</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5039</v>
+        <v>-0.2399</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6805</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7993</v>
+        <v>-0.7834</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0852</v>
+        <v>-0.4955</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7141</v>
+        <v>-0.2879</v>
       </c>
       <c r="G20" t="n">
         <v>0.6319</v>
@@ -2014,13 +2014,13 @@
         <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7328</v>
+        <v>0.2831</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4086</v>
+        <v>0.1812</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3242</v>
+        <v>0.1019</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4665</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8242</v>
+        <v>-1.5998</v>
       </c>
       <c r="E21" t="n">
         <v>-0.2819</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5423</v>
+        <v>-1.3178</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3409</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4112</v>
+        <v>-0.1867</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1125</v>
+        <v>0.112</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4528</v>
+        <v>-2.0374</v>
       </c>
       <c r="E22" t="n">
         <v>-2.3579</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0949</v>
+        <v>0.3205</v>
       </c>
       <c r="G22" t="n">
         <v>-3.5617</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.373</v>
+        <v>0.0424</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2513</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1217</v>
+        <v>0.2937</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0529</v>
+        <v>-2.8113</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0354</v>
+        <v>-2.9175</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0174</v>
+        <v>0.1062</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7134</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1797</v>
+        <v>0.0619</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1937</v>
+        <v>0.3174</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7566</v>
+        <v>-3.7617</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.258</v>
+        <v>-3.2668</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5014999999999999</v>
+        <v>-0.4949</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7122000000000001</v>
+        <v>-4.8425</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7107</v>
+        <v>-2.9218</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4229</v>
+        <v>-1.9206</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8743</v>
+        <v>-3.055</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4481</v>
+        <v>-1.5559</v>
       </c>
       <c r="L24" t="n">
-        <v>3.3224</v>
+        <v>-1.4991</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1621</v>
+        <v>-1.7875</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2626</v>
+        <v>-1.366</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1005</v>
+        <v>-0.4216</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.9585</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3842</v>
+        <v>-0.0068</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6844</v>
+        <v>-0.3536</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6998</v>
+        <v>0.3468</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
       <c r="W24" t="n">
         <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3558</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7852</v>
+        <v>-3.9525</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5027</v>
+        <v>-4.376</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2825</v>
+        <v>0.4235</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.8425</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9218</v>
+        <v>-2.7107</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9206</v>
+        <v>3.4229</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.055</v>
+        <v>1.8743</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.5559</v>
+        <v>-1.4481</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4991</v>
+        <v>3.3224</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7875</v>
+        <v>-1.1621</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.366</v>
+        <v>-1.2626</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4216</v>
+        <v>0.1005</v>
       </c>
       <c r="P25" t="n">
-        <v>1.6237</v>
+        <v>-4.639</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-6.9585</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0303</v>
+        <v>1.1883</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5895</v>
+        <v>0.5665</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5592</v>
+        <v>0.6218</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W25" t="n">
         <v>0.1418</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="26">
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-10.1581</v>
+        <v>-8.585400000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.901599999999999</v>
+        <v>-6.9018</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2563</v>
+        <v>-1.6836</v>
       </c>
       <c r="G26" t="n">
-        <v>-8.263999999999999</v>
+        <v>-8.264000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>-13.2823</v>
@@ -2461,7 +2461,7 @@
         <v>-1.7123</v>
       </c>
       <c r="L26" t="n">
-        <v>7.677499999999998</v>
+        <v>7.677499999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-14.2294</v>
@@ -2473,7 +2473,7 @@
         <v>-2.6593</v>
       </c>
       <c r="P26" t="n">
-        <v>0.000100000000000211</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q26" t="n">
         <v>-16.2367</v>
@@ -2482,13 +2482,13 @@
         <v>16.2368</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2549999999999997</v>
+        <v>1.3178</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2724000000000005</v>
+        <v>-0.2724000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.01739999999999997</v>
+        <v>1.5902</v>
       </c>
       <c r="V26" t="n">
         <v>-1.6394</v>
@@ -2497,7 +2497,7 @@
         <v>3.642</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.281400000000001</v>
+        <v>-5.2814</v>
       </c>
     </row>
   </sheetData>
